--- a/data/trans_bre/IP41-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Estudios-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 2,53</t>
+          <t>-17,72; 1,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 9,31</t>
+          <t>-9,29; 10,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 25,93</t>
+          <t>0,27; 24,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,2; 3,28</t>
+          <t>-20,9; 2,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 12,48</t>
+          <t>-10,78; 13,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 43,26</t>
+          <t>0,38; 41,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,26</t>
+          <t>-1,8; 3,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 3,65</t>
+          <t>-3,01; 3,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 3,14</t>
+          <t>-4,54; 3,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -780,17 +780,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,52</t>
+          <t>-1,89; 3,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 4,21</t>
+          <t>-3,35; 4,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 3,86</t>
+          <t>-5,33; 4,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 1,22</t>
+          <t>-7,07; 2,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 7,62</t>
+          <t>-0,72; 7,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 4,5</t>
+          <t>-6,64; 4,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -880,17 +880,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 1,31</t>
+          <t>-7,46; 2,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 8,59</t>
+          <t>-0,73; 8,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 5,15</t>
+          <t>-7,16; 4,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,97</t>
+          <t>-3,64; 0,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 3,61</t>
+          <t>-1,88; 3,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 3,35</t>
+          <t>-2,79; 3,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,06</t>
+          <t>-3,91; 1,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 4,12</t>
+          <t>-2,11; 4,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 4,0</t>
+          <t>-3,27; 4,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">

--- a/data/trans_bre/IP41-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Estudios-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,8 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,15 +531,13 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Brecha de género relativa</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -563,27 +559,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -596,8 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -627,27 +611,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-9,4%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-9,4%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
           <t>19,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -660,42 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 1,85</t>
+          <t>-18,12; 2,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 10,42</t>
+          <t>-8,53; 10,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 24,67</t>
+          <t>0,8; 25,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-20,87; 2,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 2,36</t>
+          <t>-10,12; 14,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 13,81</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 41,39</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>1,33; 44,32</t>
         </is>
       </c>
     </row>
@@ -727,27 +691,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
           <t>-0,87%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -760,42 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,25</t>
+          <t>-1,63; 3,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 3,86</t>
+          <t>-3,32; 3,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 3,35</t>
+          <t>-4,61; 3,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,73; 3,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,53</t>
+          <t>-3,63; 4,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 4,47</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-5,33; 4,04</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-5,41; 3,86</t>
         </is>
       </c>
     </row>
@@ -827,27 +771,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-3,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-3,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
           <t>-1,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -860,42 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 2,08</t>
+          <t>-7,55; 1,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 7,71</t>
+          <t>-1,42; 7,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 4,03</t>
+          <t>-6,64; 3,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,8; 2,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 2,24</t>
+          <t>-1,47; 8,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 8,8</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-7,16; 4,66</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-7,23; 4,26</t>
         </is>
       </c>
     </row>
@@ -927,27 +851,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,4%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-1,4%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
           <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -960,42 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,99</t>
+          <t>-3,82; 1,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,54</t>
+          <t>-1,73; 3,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,94</t>
+          <t>-2,75; 3,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,11; 1,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 1,07</t>
+          <t>-1,94; 4,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,06</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-3,27; 4,83</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-3,22; 4,73</t>
         </is>
       </c>
     </row>
@@ -1008,11 +912,11 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
   </mergeCells>

--- a/data/trans_bre/IP41-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 2,35</t>
+          <t>-18,15; 2,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 10,86</t>
+          <t>-9,85; 9,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 25,78</t>
+          <t>1,98; 25,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,87; 2,9</t>
+          <t>-21,2; 3,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 14,64</t>
+          <t>-11,66; 12,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 44,32</t>
+          <t>2,73; 43,26</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,27</t>
+          <t>-1,83; 3,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,6</t>
+          <t>-3,15; 3,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 3,16</t>
+          <t>-4,62; 3,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,56</t>
+          <t>-1,93; 3,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 4,14</t>
+          <t>-3,5; 4,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 3,86</t>
+          <t>-5,37; 3,86</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 1,98</t>
+          <t>-7,59; 1,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 7,56</t>
+          <t>-0,87; 7,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 3,82</t>
+          <t>-6,73; 4,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 2,2</t>
+          <t>-7,91; 1,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 8,49</t>
+          <t>-0,89; 8,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 4,26</t>
+          <t>-7,31; 5,15</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,04</t>
+          <t>-3,81; 0,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,57</t>
+          <t>-2,04; 3,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 3,89</t>
+          <t>-2,81; 3,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 1,13</t>
+          <t>-4,06; 1,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 4,1</t>
+          <t>-2,28; 4,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,73</t>
+          <t>-3,31; 4,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP41-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-7,72</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13,41</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-9,4%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,7%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-7.723205642804675</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2654951385517856</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>13.40931894427443</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.09403025591290017</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.003288507990558345</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1969500598211375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-18,15; 2,53</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,85; 9,31</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,98; 25,93</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-21,2; 3,28</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-11,66; 12,48</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,73; 43,26</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-18.15181113988175</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.850909858956197</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.97911197478111</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.2120383723570342</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.116553961176595</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0.02728204221285104</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.525965813277942</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.305829718188672</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>25.93432631095107</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.03276552998650384</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1247523637973651</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.4326246634094873</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-0,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,83; 3,26</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,15; 3,65</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,62; 3,14</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,93; 3,52</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-3,5; 4,21</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-5,37; 3,86</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.8098309325217712</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1904101395390767</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.7296411386086055</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.008651186971938823</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.00215311476349313</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.008731353605062244</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,83</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,22</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,16</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-1,29%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.827798928222367</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.14603340751851</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.61544425729966</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.01928620605970942</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.03504810089348204</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.05371230870666591</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,59; 1,22</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,87; 7,62</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,73; 4,5</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-7,91; 1,31</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,89; 8,59</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-7,31; 5,15</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.257355599322369</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.654120202601995</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.138732659666318</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.03520759972411383</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.04214197971159849</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.03863664548771827</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +767,161 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,4%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.834665661462266</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.216827390099664</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.156676649195254</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.03003791596176448</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.03498012997465925</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.01285435319813281</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,81; 0,97</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,04; 3,61</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,81; 3,35</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,06; 1,06</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-2,28; 4,12</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-3,31; 4,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.586325361003713</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.8739516506410303</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.733765117714976</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.07907798709527467</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.008945351520192844</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.07311772288371121</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.217010316814794</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.6214251966836</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.502000669845492</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.01313822535433196</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.08588913892131883</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.05146814765709434</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.291350389372303</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.812303952540705</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.438067261686359</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.01397804185036947</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.009193123854509306</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.005230318811633617</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.807112858259318</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.044475794584243</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.810084340435331</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.04060615843134109</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.02276379528030747</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.03313003466145011</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9670390298034258</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.607213622024143</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.349075401492358</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.01059845365509916</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.04124707387682734</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.03997637458596782</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +930,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
